--- a/ussi-1.xlsx
+++ b/ussi-1.xlsx
@@ -8,24 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lintaroh\Documents\ussi-timeatack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DE1ED9E-338A-4F48-B83B-847BD406C414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4E93581-EF3E-427F-9656-BBAD83DD0A8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="6">
   <si>
     <t xml:space="preserve">target_lux [lx] </t>
   </si>
@@ -37,6 +48,17 @@
   </si>
   <si>
     <t xml:space="preserve"> tr_current [A]</t>
+  </si>
+  <si>
+    <t>tr_current_hosei</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>補正値(tr_current*(4.7/100)</t>
+    <rPh sb="0" eb="3">
+      <t>ホセイチ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -419,10 +441,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="H5:P35"/>
+  <dimension ref="H4:S35"/>
   <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="12" max="12" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.83203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="5" spans="8:16">
+    <row r="4" spans="8:19">
+      <c r="L4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="8:19">
       <c r="H5" s="1">
         <v>10</v>
       </c>
@@ -435,6 +466,10 @@
       <c r="K5">
         <v>7.2799999999999998E-6</v>
       </c>
+      <c r="L5">
+        <f>(K5*4.7)/100</f>
+        <v>3.4215999999999999E-7</v>
+      </c>
       <c r="M5" s="1">
         <v>10</v>
       </c>
@@ -447,8 +482,11 @@
       <c r="P5">
         <v>1.0222300000000001E-3</v>
       </c>
-    </row>
-    <row r="6" spans="8:16">
+      <c r="S5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="8:19">
       <c r="H6" s="1">
         <v>20</v>
       </c>
@@ -461,6 +499,10 @@
       <c r="K6">
         <v>1.2480000000000001E-5</v>
       </c>
+      <c r="L6">
+        <f t="shared" ref="L6:L20" si="0">(K6*100)/4.7</f>
+        <v>2.6553191489361703E-4</v>
+      </c>
       <c r="M6" s="1" t="s">
         <v>0</v>
       </c>
@@ -474,7 +516,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="8:16">
+    <row r="7" spans="8:19">
       <c r="H7" s="1">
         <v>30</v>
       </c>
@@ -487,6 +529,10 @@
       <c r="K7">
         <v>1.9760000000000001E-5</v>
       </c>
+      <c r="L7">
+        <f t="shared" si="0"/>
+        <v>4.2042553191489357E-4</v>
+      </c>
       <c r="M7" s="1">
         <v>10</v>
       </c>
@@ -499,8 +545,12 @@
       <c r="P7">
         <v>1.0211899999999999E-3</v>
       </c>
-    </row>
-    <row r="8" spans="8:16">
+      <c r="S7">
+        <f>(P7*4.7)/100</f>
+        <v>4.7995929999999994E-5</v>
+      </c>
+    </row>
+    <row r="8" spans="8:19">
       <c r="H8" s="1">
         <v>40</v>
       </c>
@@ -513,6 +563,10 @@
       <c r="K8">
         <v>2.5999999999999998E-5</v>
       </c>
+      <c r="L8">
+        <f t="shared" si="0"/>
+        <v>5.5319148936170206E-4</v>
+      </c>
       <c r="M8" s="1" t="s">
         <v>0</v>
       </c>
@@ -525,8 +579,12 @@
       <c r="P8" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="8:16">
+      <c r="S8" t="e">
+        <f t="shared" ref="S8:S35" si="1">(P8*100)/4.7</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="9" spans="8:19">
       <c r="H9" s="1">
         <v>50</v>
       </c>
@@ -539,6 +597,10 @@
       <c r="K9">
         <v>3.4319999999999997E-5</v>
       </c>
+      <c r="L9">
+        <f t="shared" si="0"/>
+        <v>7.3021276595744671E-4</v>
+      </c>
       <c r="M9" s="1">
         <v>10</v>
       </c>
@@ -551,8 +613,12 @@
       <c r="P9">
         <v>9.9832000000000002E-4</v>
       </c>
-    </row>
-    <row r="10" spans="8:16">
+      <c r="S9">
+        <f t="shared" si="1"/>
+        <v>2.1240851063829787E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="8:19">
       <c r="H10" s="1">
         <v>60</v>
       </c>
@@ -565,6 +631,10 @@
       <c r="K10">
         <v>3.9520000000000001E-5</v>
       </c>
+      <c r="L10">
+        <f t="shared" si="0"/>
+        <v>8.4085106382978715E-4</v>
+      </c>
       <c r="M10" s="1" t="s">
         <v>0</v>
       </c>
@@ -577,8 +647,12 @@
       <c r="P10" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="8:16">
+      <c r="S10" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="11" spans="8:19">
       <c r="H11" s="1">
         <v>70</v>
       </c>
@@ -591,6 +665,10 @@
       <c r="K11">
         <v>4.888E-5</v>
       </c>
+      <c r="L11">
+        <f t="shared" si="0"/>
+        <v>1.0399999999999999E-3</v>
+      </c>
       <c r="M11" s="1">
         <v>10</v>
       </c>
@@ -603,8 +681,12 @@
       <c r="P11">
         <v>8.3609000000000005E-4</v>
       </c>
-    </row>
-    <row r="12" spans="8:16">
+      <c r="S11">
+        <f t="shared" si="1"/>
+        <v>1.7789148936170212E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="8:19">
       <c r="H12" s="1">
         <v>80</v>
       </c>
@@ -617,6 +699,10 @@
       <c r="K12">
         <v>5.4079999999999997E-5</v>
       </c>
+      <c r="L12">
+        <f t="shared" si="0"/>
+        <v>1.1506382978723403E-3</v>
+      </c>
       <c r="M12" s="1" t="s">
         <v>0</v>
       </c>
@@ -629,8 +715,12 @@
       <c r="P12" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="8:16">
+      <c r="S12" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="13" spans="8:19">
       <c r="H13" s="1">
         <v>90</v>
       </c>
@@ -643,6 +733,10 @@
       <c r="K13">
         <v>6.135E-5</v>
       </c>
+      <c r="L13">
+        <f t="shared" si="0"/>
+        <v>1.3053191489361701E-3</v>
+      </c>
       <c r="M13" s="1">
         <v>10</v>
       </c>
@@ -655,8 +749,12 @@
       <c r="P13">
         <v>7.4562000000000001E-4</v>
       </c>
-    </row>
-    <row r="14" spans="8:16">
+      <c r="S13">
+        <f t="shared" si="1"/>
+        <v>1.5864255319148937E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="8:19">
       <c r="H14" s="1">
         <v>100</v>
       </c>
@@ -669,6 +767,10 @@
       <c r="K14">
         <v>6.5510000000000001E-5</v>
       </c>
+      <c r="L14">
+        <f t="shared" si="0"/>
+        <v>1.3938297872340426E-3</v>
+      </c>
       <c r="M14" s="1" t="s">
         <v>0</v>
       </c>
@@ -681,8 +783,12 @@
       <c r="P14" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="8:16">
+      <c r="S14" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="15" spans="8:19">
       <c r="H15" s="1">
         <v>200</v>
       </c>
@@ -695,6 +801,10 @@
       <c r="K15">
         <v>1.3103E-4</v>
       </c>
+      <c r="L15">
+        <f t="shared" si="0"/>
+        <v>2.7878723404255318E-3</v>
+      </c>
       <c r="M15" s="1">
         <v>10</v>
       </c>
@@ -707,8 +817,12 @@
       <c r="P15">
         <v>7.1962000000000003E-4</v>
       </c>
-    </row>
-    <row r="16" spans="8:16">
+      <c r="S15">
+        <f t="shared" si="1"/>
+        <v>1.5311063829787233E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="8:19">
       <c r="H16" s="1">
         <v>300</v>
       </c>
@@ -721,6 +835,10 @@
       <c r="K16">
         <v>1.9342E-4</v>
       </c>
+      <c r="L16">
+        <f t="shared" si="0"/>
+        <v>4.1153191489361708E-3</v>
+      </c>
       <c r="M16" s="1" t="s">
         <v>0</v>
       </c>
@@ -733,8 +851,12 @@
       <c r="P16" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="8:16">
+      <c r="S16" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="17" spans="8:19">
       <c r="H17" s="1">
         <v>400</v>
       </c>
@@ -747,6 +869,10 @@
       <c r="K17">
         <v>2.5789999999999998E-4</v>
       </c>
+      <c r="L17">
+        <f t="shared" si="0"/>
+        <v>5.4872340425531907E-3</v>
+      </c>
       <c r="M17" s="1">
         <v>10</v>
       </c>
@@ -759,8 +885,12 @@
       <c r="P17">
         <v>6.5826000000000003E-4</v>
       </c>
-    </row>
-    <row r="18" spans="8:16">
+      <c r="S17">
+        <f t="shared" si="1"/>
+        <v>1.4005531914893619E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="8:19">
       <c r="H18" s="1">
         <v>500</v>
       </c>
@@ -773,6 +903,10 @@
       <c r="K18">
         <v>3.2861000000000001E-4</v>
       </c>
+      <c r="L18">
+        <f t="shared" si="0"/>
+        <v>6.9917021276595746E-3</v>
+      </c>
       <c r="M18" s="1" t="s">
         <v>0</v>
       </c>
@@ -785,8 +919,12 @@
       <c r="P18" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="8:16">
+      <c r="S18" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="19" spans="8:19">
       <c r="H19" s="1">
         <v>600</v>
       </c>
@@ -799,6 +937,10 @@
       <c r="K19">
         <v>3.8789E-4</v>
       </c>
+      <c r="L19">
+        <f t="shared" si="0"/>
+        <v>8.2529787234042543E-3</v>
+      </c>
       <c r="M19" s="1">
         <v>10</v>
       </c>
@@ -811,8 +953,12 @@
       <c r="P19">
         <v>9.4943999999999996E-4</v>
       </c>
-    </row>
-    <row r="20" spans="8:16">
+      <c r="S19">
+        <f t="shared" si="1"/>
+        <v>2.0200851063829788E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="8:19">
       <c r="H20" s="1">
         <v>700</v>
       </c>
@@ -825,6 +971,10 @@
       <c r="K20">
         <v>4.5652000000000003E-4</v>
       </c>
+      <c r="L20">
+        <f t="shared" si="0"/>
+        <v>9.7131914893617034E-3</v>
+      </c>
       <c r="M20" s="1" t="s">
         <v>0</v>
       </c>
@@ -837,8 +987,12 @@
       <c r="P20" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="8:16">
+      <c r="S20" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="21" spans="8:19">
       <c r="M21" s="1">
         <v>10</v>
       </c>
@@ -851,8 +1005,12 @@
       <c r="P21">
         <v>1.01599E-3</v>
       </c>
-    </row>
-    <row r="22" spans="8:16">
+      <c r="S21">
+        <f t="shared" si="1"/>
+        <v>2.16168085106383E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="8:19">
       <c r="M22" s="1" t="s">
         <v>0</v>
       </c>
@@ -865,8 +1023,12 @@
       <c r="P22" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="8:16">
+      <c r="S22" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="23" spans="8:19">
       <c r="M23" s="1">
         <v>10</v>
       </c>
@@ -879,8 +1041,12 @@
       <c r="P23">
         <v>1.0222300000000001E-3</v>
       </c>
-    </row>
-    <row r="24" spans="8:16">
+      <c r="S23">
+        <f t="shared" si="1"/>
+        <v>2.1749574468085106E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="8:19">
       <c r="M24" s="1" t="s">
         <v>0</v>
       </c>
@@ -893,8 +1059,12 @@
       <c r="P24" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="8:16">
+      <c r="S24" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="25" spans="8:19">
       <c r="M25" s="1">
         <v>10</v>
       </c>
@@ -907,8 +1077,12 @@
       <c r="P25">
         <v>1.0243100000000001E-3</v>
       </c>
-    </row>
-    <row r="26" spans="8:16">
+      <c r="S25">
+        <f t="shared" si="1"/>
+        <v>2.1793829787234043E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="8:19">
       <c r="M26" s="1" t="s">
         <v>0</v>
       </c>
@@ -921,8 +1095,12 @@
       <c r="P26" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="8:16">
+      <c r="S26" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="27" spans="8:19">
       <c r="M27" s="1">
         <v>10</v>
       </c>
@@ -935,8 +1113,12 @@
       <c r="P27">
         <v>1.0024700000000001E-3</v>
       </c>
-    </row>
-    <row r="28" spans="8:16">
+      <c r="S27">
+        <f t="shared" si="1"/>
+        <v>2.1329148936170213E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="8:19">
       <c r="M28" s="1" t="s">
         <v>0</v>
       </c>
@@ -949,8 +1131,12 @@
       <c r="P28" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="8:16">
+      <c r="S28" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="29" spans="8:19">
       <c r="M29" s="1">
         <v>10</v>
       </c>
@@ -963,8 +1149,12 @@
       <c r="P29">
         <v>6.8738000000000002E-4</v>
       </c>
-    </row>
-    <row r="30" spans="8:16">
+      <c r="S29">
+        <f t="shared" si="1"/>
+        <v>1.4625106382978724E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="8:19">
       <c r="M30" s="1" t="s">
         <v>0</v>
       </c>
@@ -977,8 +1167,12 @@
       <c r="P30" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="8:16">
+      <c r="S30" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="31" spans="8:19">
       <c r="M31" s="1">
         <v>10</v>
       </c>
@@ -991,8 +1185,12 @@
       <c r="P31">
         <v>7.4145999999999999E-4</v>
       </c>
-    </row>
-    <row r="32" spans="8:16">
+      <c r="S31">
+        <f t="shared" si="1"/>
+        <v>1.5775744680851064E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="8:19">
       <c r="M32" s="1" t="s">
         <v>0</v>
       </c>
@@ -1005,8 +1203,12 @@
       <c r="P32" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="13:16">
+      <c r="S32" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="33" spans="13:19">
       <c r="M33" s="1">
         <v>10</v>
       </c>
@@ -1019,8 +1221,12 @@
       <c r="P33">
         <v>3.0053000000000002E-4</v>
       </c>
-    </row>
-    <row r="34" spans="13:16">
+      <c r="S33">
+        <f t="shared" si="1"/>
+        <v>6.394255319148937E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="13:19">
       <c r="M34" s="1" t="s">
         <v>0</v>
       </c>
@@ -1033,8 +1239,12 @@
       <c r="P34" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="13:16">
+      <c r="S34" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="35" spans="13:19">
       <c r="M35" s="1">
         <v>10</v>
       </c>
@@ -1046,6 +1256,10 @@
       </c>
       <c r="P35">
         <v>1.01599E-3</v>
+      </c>
+      <c r="S35">
+        <f t="shared" si="1"/>
+        <v>2.16168085106383E-2</v>
       </c>
     </row>
   </sheetData>
